--- a/2025_冬ゲームコスト表.xlsx
+++ b/2025_冬ゲームコスト表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\WinterGame_2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96E91E7C-1B35-4C58-A43E-5766DD3CB438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC5C75E5-9F48-471C-AF78-D8FDB42A883E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A7566CFE-2916-499A-9B03-90D4A40E65D0}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{A7566CFE-2916-499A-9B03-90D4A40E65D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="53">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -364,6 +364,13 @@
   </si>
   <si>
     <t>ゲーム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作品展示会</t>
+    <rPh sb="0" eb="5">
+      <t>サクヒンテンジカイ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -404,7 +411,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -459,6 +466,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -500,7 +513,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -553,6 +566,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1186,6 +1205,10 @@
       <c r="M14" s="11">
         <v>29</v>
       </c>
+      <c r="O14" s="19"/>
+      <c r="P14" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A15" s="2"/>
@@ -1544,7 +1567,7 @@
       <c r="K27" s="3">
         <v>29</v>
       </c>
-      <c r="L27" s="3">
+      <c r="L27" s="18">
         <v>30</v>
       </c>
       <c r="M27" s="3">

--- a/2025_冬ゲームコスト表.xlsx
+++ b/2025_冬ゲームコスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\WinterGame_2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC5C75E5-9F48-471C-AF78-D8FDB42A883E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9662E0BF-4B1B-4F0C-863F-838C58EB32E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{A7566CFE-2916-499A-9B03-90D4A40E65D0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A7566CFE-2916-499A-9B03-90D4A40E65D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -411,7 +411,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -472,6 +472,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -535,9 +541,6 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -572,6 +575,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1038,7 +1044,7 @@
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
       <c r="O9" s="1"/>
-      <c r="P9" s="8" t="s">
+      <c r="P9" s="7" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1060,10 +1066,10 @@
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
-      <c r="M10" s="11">
+      <c r="M10" s="10">
         <v>1</v>
       </c>
-      <c r="O10" s="12"/>
+      <c r="O10" s="11"/>
       <c r="P10" t="s">
         <v>17</v>
       </c>
@@ -1076,28 +1082,28 @@
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="F11" s="3"/>
-      <c r="G11" s="11">
+      <c r="G11" s="10">
         <v>2</v>
       </c>
-      <c r="H11" s="11">
+      <c r="H11" s="10">
         <v>3</v>
       </c>
-      <c r="I11" s="11">
+      <c r="I11" s="10">
         <v>4</v>
       </c>
-      <c r="J11" s="11">
+      <c r="J11" s="10">
         <v>5</v>
       </c>
-      <c r="K11" s="11">
+      <c r="K11" s="10">
         <v>6</v>
       </c>
-      <c r="L11" s="11">
+      <c r="L11" s="10">
         <v>7</v>
       </c>
-      <c r="M11" s="11">
+      <c r="M11" s="10">
         <v>8</v>
       </c>
-      <c r="O11" s="13"/>
+      <c r="O11" s="12"/>
       <c r="P11" t="s">
         <v>18</v>
       </c>
@@ -1112,28 +1118,28 @@
       </c>
       <c r="D12" s="2"/>
       <c r="F12" s="3"/>
-      <c r="G12" s="11">
+      <c r="G12" s="10">
         <v>9</v>
       </c>
-      <c r="H12" s="11">
+      <c r="H12" s="10">
         <v>10</v>
       </c>
-      <c r="I12" s="11">
+      <c r="I12" s="10">
         <v>11</v>
       </c>
-      <c r="J12" s="11">
+      <c r="J12" s="10">
         <v>12</v>
       </c>
-      <c r="K12" s="11">
+      <c r="K12" s="10">
         <v>13</v>
       </c>
-      <c r="L12" s="11">
+      <c r="L12" s="10">
         <v>14</v>
       </c>
-      <c r="M12" s="11">
+      <c r="M12" s="10">
         <v>15</v>
       </c>
-      <c r="O12" s="14"/>
+      <c r="O12" s="13"/>
       <c r="P12" t="s">
         <v>19</v>
       </c>
@@ -1150,28 +1156,28 @@
         <v>10</v>
       </c>
       <c r="F13" s="3"/>
-      <c r="G13" s="11">
+      <c r="G13" s="10">
         <v>16</v>
       </c>
-      <c r="H13" s="11">
+      <c r="H13" s="10">
         <v>17</v>
       </c>
-      <c r="I13" s="11">
+      <c r="I13" s="10">
         <v>18</v>
       </c>
-      <c r="J13" s="11">
+      <c r="J13" s="10">
         <v>19</v>
       </c>
-      <c r="K13" s="11">
+      <c r="K13" s="10">
         <v>20</v>
       </c>
-      <c r="L13" s="11">
+      <c r="L13" s="10">
         <v>21</v>
       </c>
-      <c r="M13" s="11">
+      <c r="M13" s="10">
         <v>22</v>
       </c>
-      <c r="O13" s="16"/>
+      <c r="O13" s="15"/>
       <c r="P13" t="s">
         <v>20</v>
       </c>
@@ -1184,28 +1190,28 @@
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
       <c r="F14" s="3"/>
-      <c r="G14" s="11">
+      <c r="G14" s="10">
         <v>23</v>
       </c>
-      <c r="H14" s="11">
+      <c r="H14" s="10">
         <v>24</v>
       </c>
-      <c r="I14" s="11">
+      <c r="I14" s="10">
         <v>25</v>
       </c>
-      <c r="J14" s="11">
+      <c r="J14" s="10">
         <v>26</v>
       </c>
-      <c r="K14" s="11">
+      <c r="K14" s="10">
         <v>27</v>
       </c>
-      <c r="L14" s="11">
+      <c r="L14" s="10">
         <v>28</v>
       </c>
-      <c r="M14" s="11">
+      <c r="M14" s="10">
         <v>29</v>
       </c>
-      <c r="O14" s="19"/>
+      <c r="O14" s="18"/>
       <c r="P14" t="s">
         <v>52</v>
       </c>
@@ -1222,7 +1228,7 @@
         <v>2</v>
       </c>
       <c r="F15" s="3"/>
-      <c r="G15" s="11">
+      <c r="G15" s="10">
         <v>30</v>
       </c>
       <c r="H15" s="3"/>
@@ -1263,22 +1269,22 @@
       <c r="D17" s="2"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
-      <c r="H17" s="10">
+      <c r="H17" s="9">
         <v>1</v>
       </c>
-      <c r="I17" s="10">
+      <c r="I17" s="9">
         <v>2</v>
       </c>
-      <c r="J17" s="10">
+      <c r="J17" s="9">
         <v>3</v>
       </c>
-      <c r="K17" s="10">
+      <c r="K17" s="9">
         <v>4</v>
       </c>
-      <c r="L17" s="10">
+      <c r="L17" s="9">
         <v>5</v>
       </c>
-      <c r="M17" s="10">
+      <c r="M17" s="9">
         <v>6</v>
       </c>
     </row>
@@ -1292,25 +1298,25 @@
       </c>
       <c r="D18" s="2"/>
       <c r="F18" s="3"/>
-      <c r="G18" s="10">
+      <c r="G18" s="9">
         <v>7</v>
       </c>
-      <c r="H18" s="10">
+      <c r="H18" s="9">
         <v>8</v>
       </c>
-      <c r="I18" s="10">
+      <c r="I18" s="9">
         <v>9</v>
       </c>
-      <c r="J18" s="10">
+      <c r="J18" s="9">
         <v>10</v>
       </c>
-      <c r="K18" s="10">
+      <c r="K18" s="9">
         <v>11</v>
       </c>
-      <c r="L18" s="10">
+      <c r="L18" s="9">
         <v>12</v>
       </c>
-      <c r="M18" s="10">
+      <c r="M18" s="9">
         <v>13</v>
       </c>
     </row>
@@ -1324,25 +1330,25 @@
       </c>
       <c r="D19" s="2"/>
       <c r="F19" s="3"/>
-      <c r="G19" s="10">
+      <c r="G19" s="9">
         <v>14</v>
       </c>
-      <c r="H19" s="10">
+      <c r="H19" s="9">
         <v>15</v>
       </c>
-      <c r="I19" s="10">
+      <c r="I19" s="9">
         <v>16</v>
       </c>
-      <c r="J19" s="10">
+      <c r="J19" s="9">
         <v>17</v>
       </c>
-      <c r="K19" s="15">
+      <c r="K19" s="14">
         <v>18</v>
       </c>
-      <c r="L19" s="15">
+      <c r="L19" s="14">
         <v>19</v>
       </c>
-      <c r="M19" s="15">
+      <c r="M19" s="14">
         <v>20</v>
       </c>
     </row>
@@ -1354,25 +1360,25 @@
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
       <c r="F20" s="3"/>
-      <c r="G20" s="15">
+      <c r="G20" s="14">
         <v>21</v>
       </c>
-      <c r="H20" s="15">
+      <c r="H20" s="14">
         <v>22</v>
       </c>
-      <c r="I20" s="15">
+      <c r="I20" s="14">
         <v>23</v>
       </c>
-      <c r="J20" s="15">
+      <c r="J20" s="14">
         <v>24</v>
       </c>
-      <c r="K20" s="15">
+      <c r="K20" s="14">
         <v>25</v>
       </c>
-      <c r="L20" s="15">
+      <c r="L20" s="14">
         <v>26</v>
       </c>
-      <c r="M20" s="15">
+      <c r="M20" s="14">
         <v>27</v>
       </c>
     </row>
@@ -1388,16 +1394,16 @@
         <v>2.5</v>
       </c>
       <c r="F21" s="3"/>
-      <c r="G21" s="15">
+      <c r="G21" s="14">
         <v>28</v>
       </c>
-      <c r="H21" s="15">
+      <c r="H21" s="14">
         <v>29</v>
       </c>
-      <c r="I21" s="15">
+      <c r="I21" s="14">
         <v>30</v>
       </c>
-      <c r="J21" s="15">
+      <c r="J21" s="14">
         <v>31</v>
       </c>
       <c r="K21" s="3"/>
@@ -1440,13 +1446,13 @@
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
-      <c r="K23" s="15">
+      <c r="K23" s="14">
         <v>1</v>
       </c>
-      <c r="L23" s="15">
+      <c r="L23" s="14">
         <v>2</v>
       </c>
-      <c r="M23" s="15">
+      <c r="M23" s="14">
         <v>3</v>
       </c>
     </row>
@@ -1460,25 +1466,25 @@
       </c>
       <c r="D24" s="2"/>
       <c r="F24" s="3"/>
-      <c r="G24" s="9">
+      <c r="G24" s="19">
         <v>4</v>
       </c>
-      <c r="H24" s="9">
+      <c r="H24" s="19">
         <v>5</v>
       </c>
-      <c r="I24" s="9">
+      <c r="I24" s="19">
         <v>6</v>
       </c>
-      <c r="J24" s="9">
+      <c r="J24" s="19">
         <v>7</v>
       </c>
-      <c r="K24" s="9">
+      <c r="K24" s="19">
         <v>8</v>
       </c>
-      <c r="L24" s="9">
+      <c r="L24" s="19">
         <v>9</v>
       </c>
-      <c r="M24" s="9">
+      <c r="M24" s="19">
         <v>10</v>
       </c>
     </row>
@@ -1491,56 +1497,56 @@
       </c>
       <c r="D25" s="2"/>
       <c r="F25" s="3"/>
-      <c r="G25" s="9">
+      <c r="G25" s="19">
         <v>11</v>
       </c>
-      <c r="H25" s="9">
+      <c r="H25" s="19">
         <v>12</v>
       </c>
-      <c r="I25" s="9">
+      <c r="I25" s="19">
         <v>13</v>
       </c>
-      <c r="J25" s="9">
+      <c r="J25" s="19">
         <v>14</v>
       </c>
-      <c r="K25" s="9">
+      <c r="K25" s="19">
         <v>15</v>
       </c>
-      <c r="L25" s="3">
+      <c r="L25" s="8">
         <v>16</v>
       </c>
-      <c r="M25" s="3">
+      <c r="M25" s="8">
         <v>17</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="B26" s="17" t="s">
+      <c r="B26" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="17">
+      <c r="C26" s="16">
         <v>12</v>
       </c>
       <c r="D26" s="2"/>
       <c r="F26" s="3"/>
-      <c r="G26" s="3">
+      <c r="G26" s="8">
         <v>18</v>
       </c>
-      <c r="H26" s="3">
+      <c r="H26" s="8">
         <v>19</v>
       </c>
-      <c r="I26" s="3">
+      <c r="I26" s="8">
         <v>20</v>
       </c>
-      <c r="J26" s="3">
+      <c r="J26" s="8">
         <v>21</v>
       </c>
-      <c r="K26" s="3">
+      <c r="K26" s="8">
         <v>22</v>
       </c>
-      <c r="L26" s="7">
+      <c r="L26" s="8">
         <v>23</v>
       </c>
-      <c r="M26" s="3">
+      <c r="M26" s="8">
         <v>24</v>
       </c>
     </row>
@@ -1567,7 +1573,7 @@
       <c r="K27" s="3">
         <v>29</v>
       </c>
-      <c r="L27" s="18">
+      <c r="L27" s="17">
         <v>30</v>
       </c>
       <c r="M27" s="3">

--- a/2025_冬ゲームコスト表.xlsx
+++ b/2025_冬ゲームコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\WinterGame_2025\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\WinterGame_2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9662E0BF-4B1B-4F0C-863F-838C58EB32E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5EC36BC-4003-4950-98CD-64F24C1986A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A7566CFE-2916-499A-9B03-90D4A40E65D0}"/>
+    <workbookView xWindow="-28545" yWindow="675" windowWidth="21600" windowHeight="13440" activeTab="1" xr2:uid="{A7566CFE-2916-499A-9B03-90D4A40E65D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="53">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -332,29 +332,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ステージ設計</t>
-    <rPh sb="4" eb="6">
-      <t>セッケイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ステージ1</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>エリア1</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>エリア2</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ステージ2</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>タイトル</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -371,6 +348,38 @@
     <rPh sb="0" eb="5">
       <t>サクヒンテンジカイ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>システム効果音</t>
+    <rPh sb="4" eb="7">
+      <t>コウカオン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>選択</t>
+    <rPh sb="0" eb="2">
+      <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>決定</t>
+    <rPh sb="0" eb="2">
+      <t>ケッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>戻る</t>
+    <rPh sb="0" eb="1">
+      <t>モド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ダメ</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1213,7 +1222,7 @@
       </c>
       <c r="O14" s="18"/>
       <c r="P14" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.4">
@@ -1665,7 +1674,7 @@
     <row r="36" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A36" s="2"/>
       <c r="B36" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C36" s="2">
         <v>4</v>
@@ -1675,7 +1684,7 @@
     <row r="37" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A37" s="2"/>
       <c r="B37" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C37" s="2">
         <v>8</v>
@@ -1685,7 +1694,7 @@
     <row r="38" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A38" s="2"/>
       <c r="B38" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C38" s="2">
         <v>15</v>
@@ -1700,47 +1709,32 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8350A707-9A56-4DE4-B982-4D24FB7B3AD1}">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B7" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
-        <v>2</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
